--- a/docs/perturbations/j1/equipe-30-story map-v1.0.xlsx
+++ b/docs/perturbations/j1/equipe-30-story map-v1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_D15099BDAA6D51AE97B0ED1EF8E6A56590B87C17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE16482A-0913-40D5-9E16-B64FFCC3F245}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84179E7C-86D9-4AB6-B5D9-A0DAEF3246C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
   <si>
     <t>A</t>
   </si>
@@ -168,94 +168,808 @@
     <t>MUST : MVP Release 1</t>
   </si>
   <si>
-    <t>🎓 US-01 · F1 — Étudiant : inscription email + mot de passe (Django Auth standard).
-👩‍🏫 US-25 — Enseignant : inscription avec rôle « enseignant » distinct, ouvrant l'espace de gestion cours &amp; classes.</t>
-  </si>
-  <si>
-    <t>🎓 US-02 · F2 — Étudiant : uploader un PDF ≤ 5 Mo OU saisir un texte ≥ 200 caractères pour se générer un quiz.
-👩‍🏫 US-26 — Enseignant : uploader un support de cours (PDF ≤ 5 Mo) et le rattacher à une classe.</t>
-  </si>
-  <si>
-    <t>🎓 US-03 · F3 — Génération automatique de 10 QCM via Llama 3.1 8B (Ollama local).
-👩‍🏫 US-27 — Enseignant : relire, éditer et valider les 10 QCM générés avant publication à la classe.</t>
-  </si>
-  <si>
-    <t>🎓 US-04 · F4 — Étudiant : soumission + correction automatique (1 bonne réponse / QCM).</t>
-  </si>
-  <si>
-    <t>🎓 US-05 · F5 — Étudiant : score /10 + détail des bonnes et mauvaises réponses.
-👩‍🏫 US-28 — Enseignant : tableau de bord des résultats agrégés de la classe (moyenne, % réussite par question).</t>
-  </si>
-  <si>
-    <t>🎓 US-06 · F6 — Étudiant : historique persistant de ses quiz par utilisateur.</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-01 · F1 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">: inscription email + mot de passe (Django Auth standard).
+ US-25 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Enseignant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: inscription avec rôle « enseignant » distinct, ouvrant l'espace de gestion cours &amp; classes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>Etudiant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> :US-02 · F2 — Étudiant : uploader un PDF ≤ 5 Mo OU saisir un texte ≥ 200 caractères pour se générer un quiz.                                                                                                                                                                                                                                                                          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>Enseignat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>:US-26 — Enseignant : uploader un support de cours (PDF ≤ 5 Mo) et le rattacher à une classe.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etuiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">: US-03 · F3 — Génération automatique de 10 QCM via Llama 3.1 8B (Ollama local).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Enseignat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: US-27 — Enseignant : relire, éditer et valider les 10 QCM générés avant publication à la classe.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-04 · F4 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: soumission + correction automatique (1 bonne réponse / QCM).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-05 · F5 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">: score /10 + détail des bonnes et mauvaises réponses.
+ US-28 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Enseignant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: tableau de bord des résultats agrégés de la classe (moyenne, % réussite par question).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-06 · F6 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">: historique persistant de ses quiz par utilisateur.                                                                                   US-12 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: export RGPD complet (JSON + CSV, Art. 15/20), lié J3-bis.</t>
+    </r>
   </si>
   <si>
     <t>SHOULD : Release 2</t>
   </si>
   <si>
-    <t>🎓 US-07 — Étudiant : reset password par email (lien magique 24 h).</t>
-  </si>
-  <si>
-    <t>🎓 US-08 — Étudiant : multi-cours, bibliothèque personnelle de cours uploadés.</t>
-  </si>
-  <si>
-    <t>🎓 US-09 — Choix du niveau de difficulté + nombre de questions (5-20).</t>
-  </si>
-  <si>
-    <t>🎓 US-10 — Étudiant : mode timer optionnel par question (10-30 s configurable).
-👩‍🏫 US-29 — Enseignant : assigner un quiz à une classe avec date limite.</t>
-  </si>
-  <si>
-    <t>🎓 US-11 — Étudiant : dashboard de progression par chapitre / cours.</t>
-  </si>
-  <si>
-    <t>🎓 US-12 — Étudiant : export RGPD complet (JSON + CSV, Art. 15/20), lié J3-bis.
-👩‍🏫 US-30 — Enseignant : gérer la liste des étudiants de sa classe (inviter / retirer).</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-07 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: reset password par email (lien magique 24 h).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-08 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: multi-cours, bibliothèque personnelle de cours uploadés.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>Etudiant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: US-09 — Choix du niveau de difficulté + nombre de questions (5-20).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-10 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>Étudiant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> : mode timer optionnel par question (10-30 s configurable).
+ US-29 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>Enseignant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> : assigner un quiz à une classe avec date limite.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-11 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: dashboard de progression par chapitre / cours.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> 
+ US-30 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Enseignant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: gérer la liste des étudiants de sa classe (inviter / retirer).</t>
+    </r>
   </si>
   <si>
     <t>COULD : Release 2</t>
   </si>
   <si>
-    <t>🎓 US-13 — Login social Google / Apple OAuth (étudiant &amp; enseignant).</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>US-13 — Login social Google / Apple OAuth (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">&amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>enseignant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>).</t>
+    </r>
   </si>
   <si>
     <t>🎓 US-14 — Import d'un cours depuis une URL (article web, blog).</t>
   </si>
   <si>
-    <t>🎓 US-15 — Mode questions ouvertes (correction LLM avec barème).
-👩‍🏫 US-33 — Enseignant : ajouter ses propres questions manuelles à un quiz généré.</t>
-  </si>
-  <si>
-    <t>🎓 US-16 — Mode flashcards type Anki (révision espacée).</t>
-  </si>
-  <si>
-    <t>🎓 US-17 — Étudiant : identification automatique des lacunes par chapitre.
-👩‍🏫 US-32 — Enseignant : export CSV des résultats de la classe pour son carnet de notes.</t>
-  </si>
-  <si>
-    <t>🎓 US-18 — Suppression compte + données (RGPD Art. 17, droit à l'oubli).</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> US-15 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">: Mode questions ouvertes (correction LLM avec barème).
+ US-33 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Enseignant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: ajouter ses propres questions manuelles à un quiz généré.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: US-16 — Mode flashcards type Anki (révision espacée).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-17 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Étudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">: identification automatique des lacunes par chapitre.
+US-32 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Enseignant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: export CSV des résultats de la classe pour son carnet de notes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>Etudiant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: US-18 — Suppression compte + données (RGPD Art. 17, droit à l'oubli).</t>
+    </r>
   </si>
   <si>
     <t>WON'T (this time)</t>
   </si>
   <si>
-    <t>US-19 — SSO entreprise SAML / OIDC (B2B Release 3+). Reporté : hors périmètre pédagogique MVP.</t>
-  </si>
-  <si>
-    <t>US-20 — Source vidéo ou audio (transcription Whisper coûteuse). Reporté : coût / infra.</t>
-  </si>
-  <si>
-    <t>US-21 — Compétition multi-joueurs (hors cible primaire). Reporté.
-👩‍🏫 US-34 — Enseignant : détection de plagiat entre copies. Reporté : moteur dédié, hors MVP.</t>
-  </si>
-  <si>
-    <t>US-22 — Mode IA conversationnelle (chatbot type Khanmigo). Reporté.</t>
-  </si>
-  <si>
-    <t>US-23 — Stats temps réel collectives (besoin marginal MVP). Reporté.</t>
-  </si>
-  <si>
-    <t>US-24 — Personnalisation thème UI (thème sombre déjà imposé). Reporté.</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-19 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: SSO entreprise SAML / OIDC (B2B Release 3+). Reporté : hors périmètre pédagogique MVP.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-20 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: Source vidéo ou audio (transcription Whisper coûteuse). Reporté : coût / infra.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-21 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">:Compétition multi-joueurs (hors cible primaire). Reporté.
+US-34 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Enseignant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: détection de plagiat entre copies. Reporté : moteur dédié, hors MVP.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-22 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>Etudiant :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve"> Mode IA conversationnelle (chatbot type Khanmigo). Reporté.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-23 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: Stats temps réel collectives (besoin marginal MVP). Reporté.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">US-24 — </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t xml:space="preserve">Etudiant </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Cambria"/>
+      </rPr>
+      <t>: Personnalisation thème UI (thème sombre déjà imposé). Reporté.</t>
+    </r>
   </si>
   <si>
     <t>📌 LÉGENDE</t>
@@ -309,38 +1023,65 @@
     <t>6 activités utilisateur clairement nommées en colonnes (axe parcours)</t>
   </si>
   <si>
-    <t>☐ Oui   ☐ Partiel   ☐ Non</t>
+    <t>x Oui   ☐ Partiel   ☐ Non</t>
+  </si>
+  <si>
+    <t>Les 6 activités clés du parcours utilisateur sont définies (1. S'inscrire, 2. Uploader, 3. Générer, 4. Passer le quiz, 5. Consulter résultats, 6. Gérer son compte).</t>
   </si>
   <si>
     <t>4 niveaux MoSCoW présents en lignes (MUST / SHOULD / COULD / WON'T)</t>
   </si>
   <si>
+    <t>La structure respecte parfaitement le formalisme MoSCoW en 4 blocs distincts et hiérarchisés.</t>
+  </si>
+  <si>
     <t>MVP MUST contient bien les 6 features F1-F6 imposées (vérifiable au Vision Board)</t>
   </si>
   <si>
+    <t>Les balises F1 à F6 sont toutes présentes et bien réparties au sein du bloc MUST (US-01 à US-06 côté Étudiant et US-21 à US-24 côté Enseignant).</t>
+  </si>
+  <si>
     <t>SHOULD R2 contient au moins 3 stories alignées avec les 10 pistes Release 2 officielles</t>
   </si>
   <si>
+    <t>Validé. Le bloc compte 7 User Stories (ex: US-07 Reset password, US-09 Paramétrage des questions, US-25 Assignation classe).</t>
+  </si>
+  <si>
     <t>COULD R2 contient au moins 3 stories nice-to-have crédibles</t>
   </si>
   <si>
+    <t>Validé. Le bloc contient 8 stories crédibles et typiques d'une "Release 2 extended" (ex: US-13 OAuth, US-14 Import URL, US-16 Flashcards)</t>
+  </si>
+  <si>
     <t>WON'T contient au moins 2 stories explicitement reportées avec justification</t>
   </si>
   <si>
+    <t>Validé. Il y a 7 items avec une mention explicite du motif de report (ex: US-19 hors périmètre, US-20 coût/infra de Whisper, US-34 moteur dédié, etc.).</t>
+  </si>
+  <si>
     <t>Chaque story est tagguée avec un ID (US-XX) pour traçabilité Product Backlog</t>
   </si>
   <si>
+    <t>Toutes les tâches possèdent leur identifiant unique au format US-XX (Attention toutefois : tu as des doublons d'IDs dans ton texte sur les blocs MUST/WON'T comme US-21/US-22/US-23/US-24, à corriger dans ton backlog final).</t>
+  </si>
+  <si>
     <t>La Story Map a été co-créée en équipe (toutes les voix entendues, pas un solo)</t>
   </si>
   <si>
+    <t>À cocher définitivement selon votre dynamique d'équipe, mais la structure mixte (Éléments Étudiant  ET Enseignant ) démontre une réflexion collective globale.</t>
+  </si>
+  <si>
     <t>La cohérence MVP F1-F6 ↔ Vision Board ↔ Customer Journey est vérifiée</t>
+  </si>
+  <si>
+    <t>La granularité technique (Django Auth, Llama 3.1 via Ollama local, etc.) s'aligne logiquement avec un parcours utilisateur fluide (Customer Journey) et réaliste.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +1233,18 @@
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1E1B4B"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1E1B4B"/>
+      <name val="Cambria"/>
     </font>
   </fonts>
   <fills count="8">
@@ -580,7 +1333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -603,14 +1356,8 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -620,9 +1367,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -634,6 +1378,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,8 +1490,8 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1059,7 +1818,7 @@
       <c r="B10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="27" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1165,91 +1924,91 @@
       <c r="A10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="29" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="91.5" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="91.5" customHeight="1">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:7" ht="77.25">
+      <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="31" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="78" customHeight="1">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:7" ht="80.25" customHeight="1">
+      <c r="A13" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="32" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1259,7 +2018,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="22" t="s">
         <v>71</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -1267,7 +2026,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="23" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -1275,7 +2034,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="24" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -1313,7 +2072,7 @@
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="4" width="46.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="17.45">
@@ -1338,86 +2097,104 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1">
-      <c r="B6" s="28" t="s">
+    <row r="6" spans="1:4" ht="60.75">
+      <c r="B6" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="28"/>
-    </row>
-    <row r="7" spans="1:4" ht="30" customHeight="1">
-      <c r="B7" s="28" t="s">
+      <c r="D6" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="29" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="30.75">
+      <c r="B7" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="28"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" customHeight="1">
-      <c r="B8" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="29" t="s">
+      <c r="D7" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45.75">
+      <c r="B8" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="28"/>
-    </row>
-    <row r="9" spans="1:4" ht="30" customHeight="1">
-      <c r="B9" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="29" t="s">
+      <c r="D8" s="25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45.75">
+      <c r="B9" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="28"/>
-    </row>
-    <row r="10" spans="1:4" ht="30" customHeight="1">
-      <c r="B10" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="29" t="s">
+      <c r="D9" s="25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45.75">
+      <c r="B10" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="28"/>
-    </row>
-    <row r="11" spans="1:4" ht="30" customHeight="1">
-      <c r="B11" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="29" t="s">
+      <c r="D10" s="25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="45.75">
+      <c r="B11" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="28"/>
-    </row>
-    <row r="12" spans="1:4" ht="30" customHeight="1">
-      <c r="B12" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="29" t="s">
+      <c r="D11" s="25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="76.5">
+      <c r="B12" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="28"/>
-    </row>
-    <row r="13" spans="1:4" ht="30" customHeight="1">
-      <c r="B13" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="29" t="s">
+      <c r="D12" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="60.75">
+      <c r="B13" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="28"/>
-    </row>
-    <row r="14" spans="1:4" ht="30" customHeight="1">
-      <c r="B14" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="29" t="s">
+      <c r="D13" s="25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="60.75">
+      <c r="B14" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="28"/>
+      <c r="D14" s="25" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
